--- a/model.xlsx
+++ b/model.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\GDOforecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{8DE432E5-7D11-4A9B-8B94-6458AD2AB4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1201B948-1DA8-45A9-84CE-A9FF1499BD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="324" windowWidth="21792" windowHeight="12324"/>
+    <workbookView xWindow="32775" yWindow="1125" windowWidth="20685" windowHeight="13545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="model" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">model!$B$2:$AE$2</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">model!$B$3:$AE$3</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">model!$AH$4:$AH$8</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">model!$AH$9:$AH$59</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">model!$AH$5:$AH$9</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">model!$AH$10:$AH$60</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
@@ -32,13 +32,13 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">model!$AH$2</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">model!$AH$3</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">model!$AG$4:$AG$8</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">model!$AG$9:$AG$59</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">model!$AG$5:$AG$9</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">model!$AG$10:$AG$60</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
@@ -50,7 +50,20 @@
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -282,7 +295,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -784,11 +797,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1143,11 +1157,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH60"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1239,1090 +1253,1164 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1">
+    <row r="2" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
         <v>10</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="4">
         <v>15</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="4">
         <v>20</v>
       </c>
-      <c r="T2" s="1">
-        <v>0</v>
-      </c>
-      <c r="U2" s="1">
-        <v>0</v>
-      </c>
-      <c r="V2" s="1">
-        <v>0</v>
-      </c>
-      <c r="W2" s="1">
-        <v>0</v>
-      </c>
-      <c r="X2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="1">
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
         <v>25</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="Z2" s="4">
         <v>30</v>
       </c>
-      <c r="AA2" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <f>SUMPRODUCT(B2:AE2,B3:AE3)</f>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>10</v>
+      </c>
+      <c r="R3" s="1">
+        <v>15</v>
+      </c>
+      <c r="S3" s="1">
+        <v>20</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>25</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>30</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f>SUMPRODUCT(B3:AE3,B4:AE4)</f>
         <v>38.206494210000002</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E4" s="2">
         <v>4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F4" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G4" s="2">
         <v>10</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H4" s="2">
         <v>9</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I4" s="2">
         <v>8</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J4" s="2">
         <v>7</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K4" s="2">
         <v>6</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L4" s="2">
         <v>11</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M4" s="2">
         <v>12</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N4" s="2">
         <v>13</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O4" s="2">
         <v>14</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P4" s="2">
         <v>15</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q4" s="2">
         <v>0.27076840099999999</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R4" s="2">
         <v>0.27076840099999999</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S4" s="2">
         <v>0.27076840099999999</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T4" s="2">
         <v>0.27076840099999999</v>
       </c>
-      <c r="U3" s="2">
+      <c r="U4" s="2">
         <v>0.27076840099999999</v>
       </c>
-      <c r="V3" s="2">
+      <c r="V4" s="2">
         <v>0.12767120300000001</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W4" s="2">
         <v>0.12767120300000001</v>
       </c>
-      <c r="X3" s="2">
+      <c r="X4" s="2">
         <v>0.12767120300000001</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y4" s="2">
         <v>0.12767120300000001</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z4" s="2">
         <v>0.12767120300000001</v>
       </c>
-      <c r="AA3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="AA4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="V4">
-        <v>1</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG4">
-        <v>10</v>
-      </c>
-      <c r="AH4">
-        <f>SUMPRODUCT($B$2:$AE$2,B4:AE4)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
         <v>1</v>
       </c>
       <c r="AF5" t="s">
         <v>32</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AH5">
-        <f t="shared" ref="AH5:AH58" si="0">SUMPRODUCT($B$2:$AE$2,B5:AE5)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+        <f>SUMPRODUCT($B$3:$AE$3,B5:AE5)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="AC6">
+        <v>33</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
       <c r="AF6" t="s">
         <v>32</v>
       </c>
       <c r="AG6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AH6:AH59" si="0">SUMPRODUCT($B$3:$AE$3,B6:AE6)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
+        <v>34</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
         <v>1</v>
       </c>
       <c r="AF7" t="s">
         <v>32</v>
       </c>
       <c r="AG7">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
+        <v>35</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
         <v>1</v>
       </c>
       <c r="AF8" t="s">
         <v>32</v>
       </c>
       <c r="AG8">
+        <v>25</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG9">
         <v>30</v>
       </c>
-      <c r="AH8">
+      <c r="AH9">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG9">
-        <v>1</v>
-      </c>
-      <c r="AH9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG10">
-        <v>1</v>
-      </c>
-      <c r="AH10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG11">
-        <v>1</v>
-      </c>
-      <c r="AH11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG12">
-        <v>1</v>
-      </c>
-      <c r="AH12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG13">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG13">
-        <v>1</v>
-      </c>
-      <c r="AH13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>-10</v>
       </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>-15</v>
       </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <v>-20</v>
       </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E17">
+      <c r="E18">
         <v>-25</v>
       </c>
-      <c r="T17">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F18">
+      <c r="F19">
         <v>-30</v>
       </c>
-      <c r="U18">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G19">
+      <c r="G20">
         <v>-10</v>
       </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H20">
+      <c r="H21">
         <v>-15</v>
       </c>
-      <c r="W20">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I21">
+      <c r="I22">
         <v>-20</v>
       </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>-25</v>
       </c>
-      <c r="Y22">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>-30</v>
       </c>
-      <c r="Z23">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="L24">
+      <c r="L25">
         <v>-10</v>
       </c>
-      <c r="AA24">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="AA25">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M25">
+      <c r="M26">
         <v>-15</v>
       </c>
-      <c r="AB25">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="AB26">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N26">
+      <c r="N27">
         <v>-20</v>
       </c>
-      <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="O27">
+      <c r="O28">
         <v>-25</v>
       </c>
-      <c r="AD27">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="AD28">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P28">
+      <c r="P29">
         <v>-30</v>
       </c>
-      <c r="AE28">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="AE29">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="Q29">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="Q30">
         <v>-1</v>
       </c>
-      <c r="AF29" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29">
+      <c r="AF30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
         <f t="shared" si="0"/>
         <v>-9</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="R30">
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="R31">
         <v>-1</v>
       </c>
-      <c r="AF30" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30">
+      <c r="AF31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
         <f t="shared" si="0"/>
         <v>-14</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="S31">
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="S32">
         <v>-1</v>
       </c>
-      <c r="AF31" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31">
+      <c r="AF32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
         <f t="shared" si="0"/>
         <v>-19</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="T32">
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="T33">
         <v>-1</v>
       </c>
-      <c r="AF32" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="AF33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="U33">
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="U34">
         <v>-1</v>
       </c>
-      <c r="AF33" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="AF34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="V34">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="V35">
         <v>-1</v>
       </c>
-      <c r="AF34" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="AF35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="W35">
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="W36">
         <v>-1</v>
       </c>
-      <c r="AF35" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="AF36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="X36">
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="X37">
         <v>-1</v>
       </c>
-      <c r="AF36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG36">
-        <v>0</v>
-      </c>
-      <c r="AH36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="AF37" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="Y37">
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="Y38">
         <v>-1</v>
       </c>
-      <c r="AF37" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG37">
-        <v>0</v>
-      </c>
-      <c r="AH37">
+      <c r="AF38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
         <f t="shared" si="0"/>
         <v>-24</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="K38">
-        <v>1</v>
-      </c>
-      <c r="Z38">
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="Z39">
         <v>-1</v>
       </c>
-      <c r="AF38" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG38">
-        <v>0</v>
-      </c>
-      <c r="AH38">
+      <c r="AF39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
         <f t="shared" si="0"/>
         <v>-29</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L39">
-        <v>1</v>
-      </c>
-      <c r="AA39">
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="AA40">
         <v>-1</v>
       </c>
-      <c r="AF39" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG39">
-        <v>0</v>
-      </c>
-      <c r="AH39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="AF40" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="AB40">
+      <c r="M41">
+        <v>1</v>
+      </c>
+      <c r="AB41">
         <v>-1</v>
       </c>
-      <c r="AF40" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG40">
-        <v>0</v>
-      </c>
-      <c r="AH40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="AF41" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="N41">
-        <v>1</v>
-      </c>
-      <c r="AC41">
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="AC42">
         <v>-1</v>
       </c>
-      <c r="AF41" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="AF42" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="O42">
-        <v>1</v>
-      </c>
-      <c r="AD42">
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="AD43">
         <v>-1</v>
       </c>
-      <c r="AF42" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG42">
-        <v>0</v>
-      </c>
-      <c r="AH42">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="AF43" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="P43">
-        <v>1</v>
-      </c>
-      <c r="AE43">
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="AE44">
         <v>-1</v>
       </c>
-      <c r="AF43" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
       <c r="AF44" t="s">
         <v>38</v>
       </c>
       <c r="AG44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AH44">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="R45">
+      <c r="Q45">
         <v>1</v>
       </c>
       <c r="AF45" t="s">
@@ -2333,14 +2421,14 @@
       </c>
       <c r="AH45">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="S46">
+      <c r="R46">
         <v>1</v>
       </c>
       <c r="AF46" t="s">
@@ -2351,14 +2439,14 @@
       </c>
       <c r="AH46">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="T47">
+      <c r="S47">
         <v>1</v>
       </c>
       <c r="AF47" t="s">
@@ -2369,14 +2457,14 @@
       </c>
       <c r="AH47">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="U48">
+      <c r="T48">
         <v>1</v>
       </c>
       <c r="AF48" t="s">
@@ -2390,11 +2478,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="V49">
+      <c r="U49">
         <v>1</v>
       </c>
       <c r="AF49" t="s">
@@ -2408,11 +2496,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="W50">
+      <c r="V50">
         <v>1</v>
       </c>
       <c r="AF50" t="s">
@@ -2426,11 +2514,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="X51">
+      <c r="W51">
         <v>1</v>
       </c>
       <c r="AF51" t="s">
@@ -2444,11 +2532,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="Y52">
+      <c r="X52">
         <v>1</v>
       </c>
       <c r="AF52" t="s">
@@ -2459,14 +2547,14 @@
       </c>
       <c r="AH52">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="Z53">
+      <c r="Y53">
         <v>1</v>
       </c>
       <c r="AF53" t="s">
@@ -2477,14 +2565,14 @@
       </c>
       <c r="AH53">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AA54">
+      <c r="Z54">
         <v>1</v>
       </c>
       <c r="AF54" t="s">
@@ -2495,14 +2583,14 @@
       </c>
       <c r="AH54">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AB55">
+      <c r="AA55">
         <v>1</v>
       </c>
       <c r="AF55" t="s">
@@ -2516,11 +2604,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AC56">
+      <c r="AB56">
         <v>1</v>
       </c>
       <c r="AF56" t="s">
@@ -2534,11 +2622,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AD57">
+      <c r="AC57">
         <v>1</v>
       </c>
       <c r="AF57" t="s">
@@ -2552,11 +2640,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AE58">
+      <c r="AD58">
         <v>1</v>
       </c>
       <c r="AF58" t="s">
@@ -2570,11 +2658,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE59">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>38</v>
+      </c>
       <c r="AG59">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AH59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60">
         <v>0</v>
       </c>
     </row>
